--- a/p6_deployment/data/spain/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/p6_deployment/data/spain/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A9"/>
+  <dimension ref="A2:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -484,6 +484,34 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>ITdtTrn2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>E1Xs9lu2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>ng6idLW1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>CWcwKOO8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
